--- a/Team-Data/2008-09/3-6-2008-09.xlsx
+++ b/Team-Data/2008-09/3-6-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -688,16 +755,16 @@
         <v>7.4</v>
       </c>
       <c r="M2" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N2" t="n">
         <v>0.363</v>
       </c>
       <c r="O2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q2" t="n">
         <v>0.735</v>
@@ -706,40 +773,40 @@
         <v>10.5</v>
       </c>
       <c r="S2" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,28 +836,28 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -799,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -808,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -858,31 +925,31 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.489</v>
+        <v>0.487</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
@@ -894,13 +961,13 @@
         <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
@@ -909,19 +976,19 @@
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -936,10 +1003,10 @@
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -948,19 +1015,19 @@
         <v>17</v>
       </c>
       <c r="AM3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -975,13 +1042,13 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -1025,46 +1092,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.435</v>
+        <v>0.426</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J4" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
         <v>5.9</v>
       </c>
       <c r="M4" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
         <v>0.371</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P4" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
@@ -1076,13 +1143,13 @@
         <v>39.5</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,28 +1158,28 @@
         <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="n">
         <v>21</v>
       </c>
-      <c r="AB4" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>19</v>
       </c>
-      <c r="AF4" t="n">
-        <v>18</v>
-      </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1139,10 +1206,10 @@
         <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
         <v>16</v>
@@ -1154,13 +1221,13 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1169,10 +1236,10 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1292,7 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.451</v>
@@ -1237,31 +1304,31 @@
         <v>15.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1270,7 +1337,7 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>21.5</v>
@@ -1279,13 +1346,13 @@
         <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,7 +1364,7 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1315,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
         <v>11</v>
@@ -1327,19 +1394,19 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU5" t="n">
         <v>12</v>
       </c>
-      <c r="AT5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>13</v>
-      </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1348,13 +1415,13 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -1410,64 +1477,64 @@
         <v>78.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.393</v>
+        <v>0.389</v>
       </c>
       <c r="O6" t="n">
         <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X6" t="n">
         <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
         <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1482,7 +1549,7 @@
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
         <v>26</v>
@@ -1497,10 +1564,10 @@
         <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1515,25 +1582,25 @@
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
       </c>
       <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
         <v>6</v>
       </c>
-      <c r="AY6" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1697,7 +1764,7 @@
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -1706,13 +1773,13 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>0.635</v>
+        <v>0.645</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J8" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
@@ -1783,34 +1850,34 @@
         <v>17.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="P8" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T8" t="n">
         <v>41.1</v>
       </c>
       <c r="U8" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="V8" t="n">
         <v>15.7</v>
       </c>
       <c r="W8" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>5.9</v>
@@ -1819,25 +1886,25 @@
         <v>5.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AA8" t="n">
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.6</v>
+        <v>102.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
         <v>3</v>
       </c>
       <c r="AE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" t="n">
         <v>6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>6</v>
@@ -1846,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
         <v>13</v>
@@ -1897,7 +1964,7 @@
         <v>25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.517</v>
+        <v>0.508</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K9" t="n">
         <v>0.454</v>
@@ -1962,43 +2029,43 @@
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="N9" t="n">
         <v>0.345</v>
       </c>
       <c r="O9" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P9" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R9" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T9" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
       <c r="U9" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V9" t="n">
         <v>11.9</v>
       </c>
       <c r="W9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X9" t="n">
         <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z9" t="n">
         <v>21</v>
@@ -2007,13 +2074,13 @@
         <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2049,22 +2116,22 @@
         <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J10" t="n">
         <v>85.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
         <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="P10" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
@@ -2168,7 +2235,7 @@
         <v>41.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2189,13 +2256,13 @@
         <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.6</v>
+        <v>107.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2216,10 +2283,10 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL10" t="n">
         <v>14</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
@@ -2237,19 +2304,19 @@
         <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>15</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
@@ -2258,10 +2325,10 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
         <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>0.635</v>
+        <v>0.629</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J11" t="n">
         <v>79.59999999999999</v>
@@ -2329,22 +2396,22 @@
         <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O11" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="P11" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R11" t="n">
         <v>10.5</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T11" t="n">
         <v>42.8</v>
@@ -2353,25 +2420,25 @@
         <v>20.5</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y11" t="n">
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>99</v>
+        <v>98.7</v>
       </c>
       <c r="AC11" t="n">
         <v>3.8</v>
@@ -2380,19 +2447,19 @@
         <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
         <v>20</v>
@@ -2410,16 +2477,16 @@
         <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,13 +2495,13 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2443,16 +2510,16 @@
         <v>24</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
@@ -2613,16 +2680,16 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2780,7 +2847,7 @@
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR13" t="n">
         <v>12</v>
@@ -2792,22 +2859,22 @@
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2930,7 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
@@ -2872,16 +2939,16 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
         <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.77</v>
@@ -2890,40 +2957,40 @@
         <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
         <v>8.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2950,10 +3017,10 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
@@ -2962,7 +3029,7 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2983,7 +3050,7 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
@@ -2992,7 +3059,7 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3153,7 +3220,7 @@
         <v>28</v>
       </c>
       <c r="AT15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3171,7 +3238,7 @@
         <v>28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -3209,55 +3276,55 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
         <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>0.541</v>
+        <v>0.533</v>
       </c>
       <c r="H16" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
         <v>81</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
         <v>19.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
         <v>17</v>
       </c>
       <c r="P16" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T16" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="U16" t="n">
         <v>20.1</v>
@@ -3275,40 +3342,40 @@
         <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>11</v>
@@ -3326,34 +3393,34 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>29</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX16" t="n">
         <v>6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>27</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -3406,13 +3473,13 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
@@ -3421,10 +3488,10 @@
         <v>16.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.364</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
         <v>25.9</v>
@@ -3436,10 +3503,10 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
@@ -3448,10 +3515,10 @@
         <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y17" t="n">
         <v>4.7</v>
@@ -3463,10 +3530,10 @@
         <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3493,40 +3560,40 @@
         <v>24</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3541,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -3573,85 +3640,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.295</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="L18" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V18" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X18" t="n">
         <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA18" t="n">
         <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,10 +3730,10 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
         <v>5</v>
@@ -3684,13 +3751,13 @@
         <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="n">
         <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3702,7 +3769,7 @@
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
         <v>17</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
         <v>27</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>0.435</v>
+        <v>0.443</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3782,7 +3849,7 @@
         <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N19" t="n">
         <v>0.376</v>
@@ -3791,19 +3858,19 @@
         <v>19.3</v>
       </c>
       <c r="P19" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0.786</v>
       </c>
       <c r="R19" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S19" t="n">
         <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U19" t="n">
         <v>19.7</v>
@@ -3833,13 +3900,13 @@
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
@@ -3851,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3875,10 +3942,10 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
         <v>21</v>
@@ -3890,22 +3957,22 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>20</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4033,7 +4100,7 @@
         <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
@@ -4045,10 +4112,10 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4072,19 +4139,19 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>22</v>
@@ -4218,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4245,7 +4312,7 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
         <v>10</v>
@@ -4254,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,7 +4458,7 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
         <v>12</v>
@@ -4412,10 +4479,10 @@
         <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>12</v>
@@ -4430,13 +4497,13 @@
         <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4448,7 +4515,7 @@
         <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>0.738</v>
+        <v>0.733</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4504,34 +4571,34 @@
         <v>78.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P23" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U23" t="n">
         <v>19.2</v>
@@ -4540,28 +4607,28 @@
         <v>14.3</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
         <v>3.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB23" t="n">
         <v>102.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,7 +4643,7 @@
         <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>25</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4609,25 +4676,25 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4761,10 +4828,10 @@
         <v>18</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4788,7 +4855,7 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -4800,16 +4867,16 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY24" t="n">
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="J25" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K25" t="n">
         <v>0.502</v>
@@ -4874,25 +4941,25 @@
         <v>6.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="O25" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="P25" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R25" t="n">
         <v>10.2</v>
       </c>
       <c r="S25" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T25" t="n">
         <v>41.4</v>
@@ -4913,19 +4980,19 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.5</v>
+        <v>107.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4943,13 +5010,13 @@
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
         <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.633</v>
+        <v>0.623</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
         <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5059,16 +5126,16 @@
         <v>19</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5089,40 +5156,40 @@
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>99</v>
+      </c>
+      <c r="AC26" t="n">
         <v>3.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG26" t="n">
         <v>9</v>
       </c>
-      <c r="AF26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>8</v>
-      </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -5134,13 +5201,13 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5155,7 +5222,7 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5164,10 +5231,10 @@
         <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,13 +5243,13 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5301,10 +5368,10 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
@@ -5313,13 +5380,13 @@
         <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM27" t="n">
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
@@ -5343,10 +5410,10 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
         <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>0.672</v>
+        <v>0.667</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,10 +5478,10 @@
         <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
         <v>7.9</v>
@@ -5423,7 +5490,7 @@
         <v>20.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
         <v>15.4</v>
@@ -5438,7 +5505,7 @@
         <v>8.9</v>
       </c>
       <c r="S28" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T28" t="n">
         <v>41</v>
@@ -5447,7 +5514,7 @@
         <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
         <v>5.8</v>
@@ -5459,19 +5526,19 @@
         <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA28" t="n">
         <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5489,7 +5556,7 @@
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5534,10 +5601,10 @@
         <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>30</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
@@ -5593,25 +5660,25 @@
         <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L29" t="n">
         <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O29" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P29" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0.83</v>
@@ -5620,19 +5687,19 @@
         <v>8.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="U29" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V29" t="n">
         <v>13.1</v>
       </c>
       <c r="W29" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X29" t="n">
         <v>4.9</v>
@@ -5644,13 +5711,13 @@
         <v>19.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD29" t="n">
         <v>3</v>
@@ -5674,10 +5741,10 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM29" t="n">
         <v>22</v>
@@ -5686,7 +5753,7 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
         <v>27</v>
@@ -5698,16 +5765,16 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5716,7 +5783,7 @@
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J30" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.479</v>
+        <v>0.48</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5790,10 +5857,10 @@
         <v>0.347</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0.773</v>
@@ -5808,7 +5875,7 @@
         <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5826,16 +5893,16 @@
         <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC30" t="n">
         <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
@@ -5844,22 +5911,22 @@
         <v>8</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
         <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5889,19 +5956,19 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY30" t="n">
         <v>16</v>
       </c>
-      <c r="AY30" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>0.226</v>
+        <v>0.23</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K31" t="n">
         <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="O31" t="n">
         <v>17.4</v>
       </c>
       <c r="P31" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S31" t="n">
         <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U31" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
@@ -5999,7 +6066,7 @@
         <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
         <v>5.2</v>
@@ -6008,22 +6075,22 @@
         <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.7</v>
+        <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6035,10 +6102,10 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6053,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ31" t="n">
         <v>18</v>
@@ -6068,7 +6135,7 @@
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-6-2008-09</t>
+          <t>2009-03-06</t>
         </is>
       </c>
     </row>
